--- a/output/topology_excel/14690.xlsx
+++ b/output/topology_excel/14690.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -487,7 +487,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
         <v>10</v>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>5</v>
@@ -597,7 +597,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
         <v>11</v>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
         <v>11</v>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
         <v>11</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
@@ -707,7 +707,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
         <v>11</v>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,22 +850,22 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -875,26 +875,26 @@
         <v>92</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F21" t="n">
         <v>32</v>
@@ -902,46 +902,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Wall</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>92</v>
+        <v>403</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Wall</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>87</v>
+        <v>331</v>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -949,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>403</v>
+        <v>281</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="F25" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -993,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="F26" t="n">
         <v>11</v>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="F27" t="n">
         <v>11</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>331</v>
+        <v>245</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>281</v>
+        <v>122</v>
       </c>
       <c r="F29" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>194</v>
+        <v>330</v>
       </c>
       <c r="F31" t="n">
         <v>11</v>
@@ -1125,7 +1125,7 @@
         <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>245</v>
+        <v>400</v>
       </c>
       <c r="F32" t="n">
         <v>11</v>
@@ -1147,7 +1147,7 @@
         <v>2</v>
       </c>
       <c r="B33" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="F33" t="n">
-        <v>133</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34">
@@ -1169,7 +1169,7 @@
         <v>2</v>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F34" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
         <v>11</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>220</v>
+        <v>177</v>
       </c>
       <c r="F36" t="n">
         <v>11</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>330</v>
+        <v>243</v>
       </c>
       <c r="F37" t="n">
         <v>11</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B38" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>220</v>
+        <v>119</v>
       </c>
       <c r="F38" t="n">
         <v>11</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B39" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,15 +1290,15 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="F39" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B40" t="n">
         <v>6</v>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B41" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>278</v>
+        <v>139</v>
       </c>
       <c r="F41" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="F42" t="n">
         <v>11</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B43" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="F43" t="n">
         <v>11</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="F44" t="n">
         <v>11</v>
@@ -1422,10 +1422,10 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="F45" t="n">
-        <v>130</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
@@ -1433,7 +1433,7 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="F46" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
@@ -1455,7 +1455,7 @@
         <v>6</v>
       </c>
       <c r="B47" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>6</v>
       </c>
       <c r="B49" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>6</v>
       </c>
       <c r="B50" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="B51" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>231</v>
+        <v>139</v>
       </c>
       <c r="F51" t="n">
-        <v>187</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
@@ -1565,7 +1565,7 @@
         <v>7</v>
       </c>
       <c r="B52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>342</v>
+        <v>224</v>
       </c>
       <c r="F52" t="n">
         <v>11</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B53" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="F53" t="n">
         <v>11</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B54" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F54" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B55" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="F55" t="n">
         <v>11</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B56" t="n">
+        <v>8</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>32</v>
+      </c>
+      <c r="F56" t="n">
         <v>16</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="n">
-        <v>128</v>
-      </c>
-      <c r="F56" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B57" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,18 +1686,18 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="F57" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B58" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,18 +1708,18 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>32</v>
+        <v>223</v>
       </c>
       <c r="F58" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,18 +1730,18 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="F59" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,18 +1752,18 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="F60" t="n">
-        <v>184</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B61" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>343</v>
+        <v>119</v>
       </c>
       <c r="F61" t="n">
         <v>11</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B62" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,18 +1796,18 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F62" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B63" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,18 +1818,18 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F63" t="n">
-        <v>11</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B64" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>145</v>
+        <v>342</v>
       </c>
       <c r="F64" t="n">
         <v>11</v>
@@ -1848,11 +1848,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
+        <v>10</v>
+      </c>
+      <c r="B65" t="n">
         <v>17</v>
       </c>
-      <c r="B65" t="n">
-        <v>19</v>
-      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1862,15 +1862,15 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="F65" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B66" t="n">
         <v>21</v>
@@ -1884,18 +1884,18 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>119</v>
+        <v>231</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B67" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1906,32 +1906,164 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>32</v>
+        <v>343</v>
       </c>
       <c r="F67" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B68" t="n">
+        <v>18</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>128</v>
+      </c>
+      <c r="F68" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>13</v>
+      </c>
+      <c r="B69" t="n">
+        <v>14</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>183</v>
+      </c>
+      <c r="F69" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>14</v>
+      </c>
+      <c r="B70" t="n">
         <v>22</v>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="n">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
         <v>183</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F70" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>15</v>
+      </c>
+      <c r="B71" t="n">
+        <v>16</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>183</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>16</v>
+      </c>
+      <c r="B72" t="n">
+        <v>24</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>183</v>
+      </c>
+      <c r="F72" t="n">
         <v>32</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="n">
+        <v>13</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>183</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" t="n">
+        <v>15</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>183</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/14690.xlsx
+++ b/output/topology_excel/14690.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>281</v>
       </c>
       <c r="F24" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -1161,7 +1161,7 @@
         <v>278</v>
       </c>
       <c r="F33" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -1821,7 +1821,7 @@
         <v>231</v>
       </c>
       <c r="F63" t="n">
-        <v>187</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
@@ -1887,7 +1887,7 @@
         <v>231</v>
       </c>
       <c r="F66" t="n">
-        <v>184</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
